--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G10-G11.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G10-G11.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Biomoléculas (carbohidratos); ambos FUERA del marco AUSS (biomoléculas en detalle)</t>
+          <t>fusión: ambos temas trabajan Biomoléculas (carbohidratos); ambos FUERA del marco AUSS (biomoléculas en detalle); quitar_conceptos: la química de los carbohidratos (grupos funcionales, enlace glucosídico) se trabaja en Química 11.°, unidad 11</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Biomoléculas (lípidos); ambos FUERA del marco AUSS</t>
+          <t>fusión: ambos temas trabajan Biomoléculas (lípidos); ambos FUERA del marco AUSS; quitar_conceptos: la química de los lípidos (esterificación e hidrólisis) se trabaja en Química 11.°, unidad 11</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -1561,6 +1561,60 @@
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>El tema es física sin objetivo de ACARA. Se reformula, sin gastar presupuesto, para sumar la osmorregulación en animales acuáticos, débil en el ciclo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>G10-BIO-U1-1.3, G10-BIO-U1-1.6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Biomoléculas</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1.3. Descripción de los polisacáridos de reserva y estructurales y su función en los seres vivos. | 1.6. Descripción de las funciones de los lípidos en los seres vivos (reserva de energía, membranas, señales).</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Relaciona almidón, glucógeno y celulosa con su función de reserva o de sostén en plantas y animales. | Explica con ejemplos la función energética, estructural y reguladora de los lípidos sin recurrir a mecanismos de reacción.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Biomoléculas</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>revisión Química 10.°–11.°: las etiquetas secundarias fijan «Química de los carbohidratos» y «Química de los lípidos» en 10.°, antes de «Grupos funcionales» y «Esterificación e hidrólisis» (11.°): errores de secuencia de confianza alta; la química orgánica de las biomoléculas queda en Química 11.°, unidad 11</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Biología trata las biomoléculas de forma descriptiva (estructura-función). Se reformulan los temas para que no trabajen la química orgánica de carbohidratos y lípidos, que corresponde a Química 11.°. No cambia el número de temas.</t>
         </is>
       </c>
     </row>
